--- a/test/test.xlsx
+++ b/test/test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\赵家麒\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\赵家麒\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8503BFAB-3069-46BF-B830-CECAECACD98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB304DB0-B051-45D2-9053-64E7296ED9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6400" yWindow="4110" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="test_case(测试结果)" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>question</t>
   </si>
@@ -314,6 +314,14 @@
   </si>
   <si>
     <t>What is the follow-up for 6-8 mm nodules</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>doc_name</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>a.pdf</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -692,15 +700,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.81640625" customWidth="1"/>
-    <col min="2" max="2" width="20.36328125" customWidth="1"/>
-    <col min="5" max="5" width="28.36328125" customWidth="1"/>
+    <col min="2" max="3" width="20.36328125" customWidth="1"/>
+    <col min="6" max="6" width="28.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -708,29 +716,35 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
